--- a/guidance_data.xlsx
+++ b/guidance_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a59feb46c0328b82/デスクトップ/生徒指導提要/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6291A032-73E5-4E49-B7C7-ABD5C27F0A49}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA13C5A3-B668-4386-816F-7FF548BFCDE8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="19845" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>不登校傾向（週明けの欠席が続く）</t>
   </si>
@@ -97,6 +97,24 @@
   </si>
   <si>
     <t>生徒指導提要 第10章 10.1.3 不登校児童生徒への支援の方向性</t>
+  </si>
+  <si>
+    <t>生徒同士の不満や人間関係のもつれがあり、教員立ち会いのもとで話し合いを行ったが、途中で口調が荒くなったり、相手を責める言い方になったりする場面がある。場合によっては感情が高ぶり、身体接触や暴力行為に発展することもある。</t>
+  </si>
+  <si>
+    <t>「仲直りさせること」を目的にせず、安全確保・事実確認・責任の整理・再発防止を目的にする。暴力や身体接触があった場合は、人間関係の問題とは切り分けて、安全に関わる重大な行為として扱う。</t>
+  </si>
+  <si>
+    <t>話し合いの前に、目的とルールを明確にする。「相手を責める場ではなく、今後どうするかを確認する場」と伝える。話す内容は「嫌だったこと」よりも「今後改善してほしいこと」に整理させる。口調が荒くなったら一度止め、必要に応じて個別聞き取りに切り替える。</t>
+  </si>
+  <si>
+    <t>生徒同士を自由に言い合わせる。過去の不満を掘り返させる。どちらが悪いかをその場で決めようとする。「お互い様」「謝ったから終わり」で済ませる。暴力行為と相手の言動を相殺する。口調が荒くなっているのに話し合いを続ける。</t>
+  </si>
+  <si>
+    <t>手を出した行為は理由に関係なく不適切であると本人が認める。言葉や態度で相手を追い詰めた側にも改善点を確認する。ただし、暴力と相手の言動は別問題として整理する。今後は、直接ぶつけ合わず、教員を通して整理すること、感情が高ぶったら場を離れること、身体接触をしないことを具体的に約束させる。</t>
+  </si>
+  <si>
+    <t>「今からする話し合いは、相手を責めるためではなく、これから同じことを起こさないための確認です。」「嫌だったことは言っていい。ただし、文句や人格否定ではなく、今後どうしてほしいかで伝えます。」「相手が何を言ったとしても、手を出すことは絶対に認められません。」「言葉で追い詰めることも、人間関係を悪くする行動です。」「もう無理だと思ったら、その場を離れる、先生に止めてもらう、今は話せませんと言う。この中から選びます。」「謝って終わりではなく、次に同じ場面になったときにどうするかまで決めます。」</t>
   </si>
 </sst>
 </file>
@@ -425,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -495,6 +513,26 @@
       </c>
       <c r="G3" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/guidance_data.xlsx
+++ b/guidance_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a59feb46c0328b82/デスクトップ/生徒指導提要/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA13C5A3-B668-4386-816F-7FF548BFCDE8}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F6FD9B2-1AA8-4A73-9D3E-2358733D77A1}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="19845" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>不登校傾向（週明けの欠席が続く）</t>
   </si>
@@ -115,6 +115,16 @@
   </si>
   <si>
     <t>「今からする話し合いは、相手を責めるためではなく、これから同じことを起こさないための確認です。」「嫌だったことは言っていい。ただし、文句や人格否定ではなく、今後どうしてほしいかで伝えます。」「相手が何を言ったとしても、手を出すことは絶対に認められません。」「言葉で追い詰めることも、人間関係を悪くする行動です。」「もう無理だと思ったら、その場を離れる、先生に止めてもらう、今は話せませんと言う。この中から選びます。」「謝って終わりではなく、次に同じ場面になったときにどうするかまで決めます。」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生徒指導提要 </t>
+    <rPh sb="0" eb="2">
+      <t>セイト</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>シドウテイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -534,6 +544,9 @@
       <c r="F4" t="s">
         <v>26</v>
       </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/guidance_data.xlsx
+++ b/guidance_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a59feb46c0328b82/デスクトップ/生徒指導提要/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F6FD9B2-1AA8-4A73-9D3E-2358733D77A1}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBE5429F-D2CD-46E9-B477-60F21547E397}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="19845" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>不登校傾向（週明けの欠席が続く）</t>
   </si>
@@ -125,6 +125,24 @@
       <t>シドウテイヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>教員に対するからかい・いじり・茶化しが続き、注意してもやまない。授業中や休み時間に、教員の言動・見た目・口調・失敗などを笑いにし、周囲も笑うことでエスカレートしている。</t>
+  </si>
+  <si>
+    <t>「冗談で済ませない」「人を傷つける行為として扱う」「集団の空気を止める」ことを基本にする。教員個人の好き嫌いではなく、学校生活のルール・人権・安心して過ごせる環境の問題として指導する。</t>
+  </si>
+  <si>
+    <t>まずその場では短く止める。長く説教せず、「今の発言はからかいなので止めます」と明確に伝える。その後、個別または少人数で、何を言ったか、相手がどう感じるか、周囲が笑うことで何が起きるかを確認する。本人の意図よりも、行為の影響に目を向けさせる。</t>
+  </si>
+  <si>
+    <t>「先生が傷ついたから謝れ」と感情だけで迫ること。全体の前で長時間叱責すること。からかいに乗って笑いにすること。「冗談ならいい」と曖昧にすること。誰が言ったか探しだけになり、周囲で笑った生徒の責任を扱わないこと。</t>
+  </si>
+  <si>
+    <t>教員に対するからかいを、相手を下げる行為として理解させる。本人が「冗談のつもりでも、相手や周囲に与える影響がある」と認識し、今後は言わない・乗らない・広げない行動を取れるようにする。必要に応じて保護者共有や学年全体でのルール確認につなげる。</t>
+  </si>
+  <si>
+    <t>「今のは笑いではなく、相手を下げる言い方です。止めます。」「先生だから我慢して当然、ではありません。人に言ってよいことと悪いことがあります。」「冗談のつもりでも、相手が嫌な思いをしたり、周りがまねしたりするなら指導します。」「言った人だけでなく、笑って広げた人も同じ空気を作っています。」「今日確認したいのは、先生が怒ったかどうかではなく、人をからかう行動をこれから止められるかです。」</t>
   </si>
 </sst>
 </file>
@@ -453,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -546,6 +564,26 @@
       </c>
       <c r="G4" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/guidance_data.xlsx
+++ b/guidance_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a59feb46c0328b82/デスクトップ/生徒指導提要/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBE5429F-D2CD-46E9-B477-60F21547E397}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70192A2F-CBC7-4CB4-9637-2E34C5953803}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>不登校傾向（週明けの欠席が続く）</t>
   </si>
@@ -143,6 +143,24 @@
   </si>
   <si>
     <t>「今のは笑いではなく、相手を下げる言い方です。止めます。」「先生だから我慢して当然、ではありません。人に言ってよいことと悪いことがあります。」「冗談のつもりでも、相手が嫌な思いをしたり、周りがまねしたりするなら指導します。」「言った人だけでなく、笑って広げた人も同じ空気を作っています。」「今日確認したいのは、先生が怒ったかどうかではなく、人をからかう行動をこれから止められるかです。」</t>
+  </si>
+  <si>
+    <t>全校集会や学年集会などで床に座る場面において、無意識に手を後ろについて足を前に伸ばしてしまい、集団の中で姿勢が崩れて見える状況。本人に反抗的な意図はなく、癖や楽な姿勢として出てしまっている場合が多い。</t>
+  </si>
+  <si>
+    <t>まずは「態度が悪い」と決めつけず、無意識の癖として扱う。集会は話を聞く場であり、周囲から見た姿勢も大切であることを伝える。叱るよりも、望ましい座り方を具体的に確認し、本人が気づいて直せるようにする。</t>
+  </si>
+  <si>
+    <t>集会後など落ち着いた場面で短く個別に確認する。「わざとではないと思うけど」と前置きし、手を後ろにつく・足を伸ばす姿勢が周囲からどう見えるかを一緒に考える。そのうえで、あぐら、体育座り、膝を立てずに座るなど、学校で求める座り方を具体的に確認する。必要に応じて、次の集会前に事前に声をかける。</t>
+  </si>
+  <si>
+    <t>みんなの前で強く注意する。「やる気がない」「態度が悪い」「だらしない」と人格や意欲に結びつけて責める。本人が無意識にしていることを、反抗や挑発として扱う。正しい座り方を示さずに「ちゃんと座れ」だけで終わらせる。</t>
+  </si>
+  <si>
+    <t>本人が自分の癖に気づき、集会の場にふさわしい姿勢を自分で意識して直せるようになること。注意されたから直すのではなく、「話を聞く場では周囲から見える姿勢も大切」という理解をもつこと。</t>
+  </si>
+  <si>
+    <t>「わざとじゃないと思うけど、集会のときに手を後ろについて足が伸びていることがあるよ」「その座り方だと、話を聞く気がないように見えてしまうことがある」「集会のときは、手を前にして足を伸ばさない座り方を意識しよう」「次の集会では、最初に自分で姿勢を確認してみよう」「気づければ直せることだから、まずはそこを意識しよう」</t>
   </si>
 </sst>
 </file>
@@ -471,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -584,6 +602,26 @@
       </c>
       <c r="F5" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/guidance_data.xlsx
+++ b/guidance_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a59feb46c0328b82/デスクトップ/生徒指導提要/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70192A2F-CBC7-4CB4-9637-2E34C5953803}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2F03C6-E654-4E55-8BA0-29DA2F4EBA31}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>不登校傾向（週明けの欠席が続く）</t>
   </si>
@@ -161,6 +161,24 @@
   </si>
   <si>
     <t>「わざとじゃないと思うけど、集会のときに手を後ろについて足が伸びていることがあるよ」「その座り方だと、話を聞く気がないように見えてしまうことがある」「集会のときは、手を前にして足を伸ばさない座り方を意識しよう」「次の集会では、最初に自分で姿勢を確認してみよう」「気づければ直せることだから、まずはそこを意識しよう」</t>
+  </si>
+  <si>
+    <t>授業への参加意欲が低く、声かけがあってようやく例題を1題写す程度の状態。基本的には課題に取り組まず、周囲とおしゃべりをしたり、机に伏せたりして授業時間を過ごしている。</t>
+  </si>
+  <si>
+    <t>「やる気がない」と決めつけず、まずは授業参加のハードルを下げる。全てを一気にやらせるのではなく、「今日はここまでできればよい」という最低ラインを明確にし、小さな参加を積み重ねる。周囲への影響がある場合は、本人の困り感と学級への影響を分けて対応する。</t>
+  </si>
+  <si>
+    <t>授業中は短く具体的に声をかける。放課後や別時間に、「なぜやらないのか」を責めるのではなく、「どこからならできそうか」「何があると始めやすいか」を確認する。本人が取り組める最小単位を一緒に決め、次回の授業で実行できる行動目標にする。</t>
+  </si>
+  <si>
+    <t>「やる気がないなら出ていけ」「みんなはやっているのに」など、人格や態度を責める言い方。長時間の説教。いきなり全問取り組ませようとする対応。おしゃべりや伏せる行動だけを強く叱り、授業に入れない理由を確認しない対応。できていない部分だけを全体の前で指摘すること。</t>
+  </si>
+  <si>
+    <t>授業中に完全に集中し続けることではなく、まずは「授業の最初にプリントを出す」「例題を1題写す」「練習問題を1問解く」など、本人が授業に参加する行動を安定して取れるようにする。最終的には、声かけがなくても自分で取り組み始め、周囲の学習を妨げない状態を目指す。</t>
+  </si>
+  <si>
+    <t>「全部やらなくていい。まず例題1だけ写そう」「ここまでできたら今日は合格にしよう」「今は書くところから始めよう」「分からないなら、写すだけでも授業に入っていることになるよ」「おしゃべりは一度止めて、ここだけ一緒にやろう」「伏せる前に、1行だけ書いてみよう」</t>
   </si>
 </sst>
 </file>
@@ -489,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -622,6 +640,26 @@
       </c>
       <c r="F6" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/guidance_data.xlsx
+++ b/guidance_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a59feb46c0328b82/デスクトップ/生徒指導提要/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E2F03C6-E654-4E55-8BA0-29DA2F4EBA31}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_F25DC773A252ABDACC10482001D95D825ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0C72092-D362-4396-B5E6-7F97F25D2509}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>不登校傾向（週明けの欠席が続く）</t>
   </si>
@@ -179,6 +179,39 @@
   </si>
   <si>
     <t>「全部やらなくていい。まず例題1だけ写そう」「ここまでできたら今日は合格にしよう」「今は書くところから始めよう」「分からないなら、写すだけでも授業に入っていることになるよ」「おしゃべりは一度止めて、ここだけ一緒にやろう」「伏せる前に、1行だけ書いてみよう」</t>
+  </si>
+  <si>
+    <t>授業中に、授業とは関係のない作業をしており、注意してもすぐに直らない場面。学習への参加が弱く、本人の中で「今やるべきこと」の優先順位が下がっている状態。</t>
+  </si>
+  <si>
+    <t>まずは感情的に叱るのではなく、「今は何をする時間か」を明確にする。行動を責めるより、授業に戻るための具体的な行動を示す。繰り返す場合は、本人の困り感や理由を確認し、授業参加のハードルを下げる。</t>
+  </si>
+  <si>
+    <t>全体の前で強く叱責する。理由を聞かずに「やる気がない」と決めつける。注意に従わないことだけを問題にして、授業内容への戻し方を示さない。長時間説教して、授業参加の機会をさらに失わせる。</t>
+  </si>
+  <si>
+    <t>授業中に「今やるべきこと」を理解し、別作業をやめて授業の活動に戻れること。すべてを完璧にやらせることよりも、まずは教科書を開く、問題を1問解く、説明を聞くなど、授業参加の行動を増やすこと。</t>
+  </si>
+  <si>
+    <t>「今はこの作業をいったん止めて、ここを一緒に見よう」「まずは1問だけやってみよう」「今やることはこれです。終わったら確認します」「別のことをしたくなる理由があるなら、あとで聞くね。今はここに戻ろう」「全部でなくていいから、まずここから始めよう」</t>
+  </si>
+  <si>
+    <t>授業中は短く具体的に声をかける。必要以上にやり取りを長引かせず、「今やること」を一点に絞って伝える。授業後に個別で、なぜ別作業をしていたのか、授業に戻るために何があればよいかを確認する。本人が選べる小さな行動目標を一緒に決める。教科書・ノート・プリントが手元にある
+今どこをやっているかが分かる
+何をすればよいかが一つに絞られている
+問題が難しすぎず、最初の一問だけならできそう
+先生が横で一度説明してくれる
+周囲の目が気にならない形で声をかけてもらえる
+別作業を片付ける場所やタイミングがある
+気持ちを切り替える短い時間がある
+「授業に戻るためには何が必要？」
+と聞くよりも、中学生には
+「どうしたら授業に戻れそう？」
+「教科書を出すところからならできる？」
+「今どこをやっているか分かれば戻れそう？」
+「最初の1問だけ一緒にやればできそう？」
+くらいに具体的に聞いた方がいいです。</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -221,8 +254,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -507,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="25.625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -660,6 +694,26 @@
       </c>
       <c r="F7" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
